--- a/data/metadata/public_datasets_metadata.xlsx
+++ b/data/metadata/public_datasets_metadata.xlsx
@@ -19,13 +19,7 @@
     <sheet state="visible" name="Repackaging (MedSAM MRI)" sheetId="14" r:id="rId18"/>
     <sheet state="visible" name="Excluded Datasets" sheetId="15" r:id="rId19"/>
   </sheets>
-  <definedNames>
-    <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">Challenges!$A$1:$X$59</definedName>
-    <definedName hidden="1" localSheetId="4" name="_xlnm._FilterDatabase">'Well-Cited Datasets'!$A$1:$Z$31</definedName>
-    <definedName hidden="1" localSheetId="6" name="_xlnm._FilterDatabase">'Data Collection (Stanford AIMI)'!$A$1:$S$14</definedName>
-    <definedName hidden="1" localSheetId="8" name="_xlnm._FilterDatabase">'Data Collection (MIDRC)'!$A$1:$K$25</definedName>
-    <definedName hidden="1" localSheetId="10" name="_xlnm._FilterDatabase">'Repackaging (Secondary)'!$A$1:$P$27</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr/>
 </workbook>
 </file>
@@ -33,144 +27,31 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={15d0c6b0-d221-41d9-a5ef-8b7f2fc1ae45}</author>
-    <author>tc={18f530a5-07e4-4904-9737-70895410aa30}</author>
-    <author>tc={30657624-dd6e-49e4-bbc4-9105cbd1ff54}</author>
-    <author>tc={580d2974-de9e-43ff-8fa9-81c3e9fd3ae6}</author>
-    <author>tc={68402715-6c3d-4a13-a4cf-fc05c4c49e47}</author>
-    <author>tc={6aa35232-dc3e-4fc3-88a9-b16de6dee409}</author>
-    <author>tc={77fce280-284f-4d10-bfe6-e9b0c082d4a1}</author>
-    <author>tc={79d54332-c935-4812-bf26-25afe4416f4e}</author>
-    <author>tc={81dc5f9c-873d-485a-9f36-f9d6447bdaa4}</author>
-    <author>tc={86244669-eb33-4030-975e-5bfdeaf87de5}</author>
-    <author>tc={880f0d25-4437-4265-afa4-de1d229c0ad5}</author>
-    <author>tc={8b1ec243-3d92-4415-af7f-b2154f4f6ecb}</author>
-    <author>tc={929cb761-c6e6-4b7b-96d7-9199a3702c2f}</author>
-    <author>tc={a24a3e3f-c726-441a-8ae6-632cc60e9b00}</author>
-    <author>tc={aa5e53d1-26ac-4392-88ce-31414d0c5d3b}</author>
-    <author>tc={af370e31-5eca-4558-9048-99ee6d800e21}</author>
-    <author>tc={b7fbe182-3cca-4c18-a3cf-50c0bc3b2646}</author>
-    <author>tc={cb45dbb0-6787-444b-ae33-439c2583991f}</author>
-    <author>tc={d9d16971-1beb-4741-ba6b-b0d7ab144091}</author>
-    <author>tc={e66f9bd8-27dc-437a-96bd-1e57ed80acda}</author>
-    <author>tc={ed3d849b-2462-40f9-9215-6a9636e6d22b}</author>
-    <author>tc={efffed77-dbe3-45f6-a2a9-a0ff09cc82ef}</author>
+    <author>tc={000797c7-a047-48f0-b911-83900582991f}</author>
+    <author>tc={0c167707-c772-4a5c-8224-9ecfbe1f2637}</author>
+    <author>tc={101a2eef-98f5-4e94-a791-55e3dc553754}</author>
+    <author>tc={17326ac0-dbee-4866-bd9d-49536ff6670c}</author>
+    <author>tc={1cb3283f-b2e6-4f63-8c45-5812449d6898}</author>
+    <author>tc={27924f17-c1d0-4d2f-b29d-b0790aafc430}</author>
+    <author>tc={2d2f55a4-bace-4147-9175-f4741b6542ef}</author>
+    <author>tc={33c636e8-f411-4087-b4c3-60e1bad5b313}</author>
+    <author>tc={3b91a783-c71a-41a1-be39-c75e49de478d}</author>
+    <author>tc={4171f2a8-c9c8-48b6-b6f8-fcd776a3d527}</author>
+    <author>tc={474565d4-43ba-449b-be22-266d57262e6d}</author>
+    <author>tc={4c7ea26c-267f-4ae4-8c05-6de7fa405797}</author>
+    <author>tc={62f45e37-0bce-43a8-892f-4c22e2b88192}</author>
+    <author>tc={82124f08-9139-4b66-8529-549d7747dcce}</author>
+    <author>tc={85357102-e5c2-44f9-92d4-04e51e318dbd}</author>
+    <author>tc={9888ea57-0164-4785-823d-e7f82b2fb8d5}</author>
+    <author>tc={a28080ca-20e2-4398-a9c7-e8bd9944d043}</author>
+    <author>tc={a450042a-5129-4cb8-9f19-4ff320540b5e}</author>
+    <author>tc={b6eab8f9-53cf-42cf-8c9e-62fb0cbee2dd}</author>
+    <author>tc={c03a7816-4919-4fd0-b98e-97d48d832608}</author>
+    <author>tc={d3327184-608f-4a96-bead-92b06806ba90}</author>
+    <author>tc={da4efe22-4942-4752-9c86-b642520c0ab0}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{15d0c6b0-d221-41d9-a5ef-8b7f2fc1ae45}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Awaiting review
-</t>
-      </text>
-    </comment>
-    <comment authorId="1" xr:uid="{18f530a5-07e4-4904-9737-70895410aa30}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	So I think we should group "Research access" and "Public data" since a lot of these are actually research access but they are public in the sense that they are accessible for research?
-Reply:
-	Yeah, I think for our purposes/analyses, public and research data is the same
-1 total reaction
-Lauren Erdman reacted with 👍 at 2024-12-20 21:17 PM
-</t>
-      </text>
-    </comment>
-    <comment authorId="2" xr:uid="{30657624-dd6e-49e4-bbc4-9105cbd1ff54}" ref="H13">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	@stanley.z.hua@gmail.com I can never remember or find if chexpert is adult only. Do you mind filling this in?
-Reply:
-	Done!
-</t>
-      </text>
-    </comment>
-    <comment authorId="3" xr:uid="{580d2974-de9e-43ff-8fa9-81c3e9fd3ae6}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Same paper as above
-</t>
-      </text>
-    </comment>
-    <comment authorId="4" xr:uid="{68402715-6c3d-4a13-a4cf-fc05c4c49e47}" ref="J4">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Age not mentioned for most datasets, except one with fetal gestational age
-</t>
-      </text>
-    </comment>
-    <comment authorId="5" xr:uid="{6aa35232-dc3e-4fc3-88a9-b16de6dee409}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Consider removing because of sample-size
-</t>
-      </text>
-    </comment>
-    <comment authorId="6" xr:uid="{77fce280-284f-4d10-bfe6-e9b0c082d4a1}" ref="H16">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	ATLAS v2.0 is used for testing. It's aggregated from other studies, and the age is unknown
-</t>
-      </text>
-    </comment>
-    <comment authorId="7" xr:uid="{79d54332-c935-4812-bf26-25afe4416f4e}" ref="I65">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Seems like it is public based on other uses of this data but the links don't work and I can't find a way to access it online...
-Reply:
-	Can't find it either, and it seems like the authors are from the same institution (Tel Aviv university) where the data came from, so I'd guess it's private?
-Also it's an fMRI dataset, which is outside our inclusion criteria, but we can include this in extra analysis
-</t>
-      </text>
-    </comment>
-    <comment authorId="8" xr:uid="{81dc5f9c-873d-485a-9f36-f9d6447bdaa4}" ref="F31">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	@stanley.z.hua@gmail.com Do you know if any of these have children?
-Reply:
-	Yes, CheXpert contains very little children! but it's unlikely that the COVID CXR dataset has any age annotation (so Unknown might be better? not sure)
-</t>
-      </text>
-    </comment>
-    <comment authorId="9" xr:uid="{86244669-eb33-4030-975e-5bfdeaf87de5}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	The ABIDE dataset contains pediatric patients
-</t>
-      </text>
-    </comment>
-    <comment authorId="10" xr:uid="{880f0d25-4437-4265-afa4-de1d229c0ad5}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Dataset-Level Metadata is used to estimate the proportion of datasets with age mentioned.
-Patient-Level Metadata is used to estimate the percentage of Peds vs. Adult data.
-Patient-Level Metadata (NeuroBagel): https://query.neurobagel.org/?node=OpenNeuro
-Dataset-Level Metadata: https://docs.google.com/spreadsheets/u/0/d/1rsVlKg0vBzkx7XUGK4joky9cM8umtkQRpJ2Y-5d6x7c/htmlview#
-</t>
-      </text>
-    </comment>
-    <comment authorId="11" xr:uid="{8b1ec243-3d92-4415-af7f-b2154f4f6ecb}" ref="A1">
+    <comment authorId="0" xr:uid="{000797c7-a047-48f0-b911-83900582991f}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -179,16 +60,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="12" xr:uid="{929cb761-c6e6-4b7b-96d7-9199a3702c2f}" ref="C7">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Same paper
-</t>
-      </text>
-    </comment>
-    <comment authorId="13" xr:uid="{a24a3e3f-c726-441a-8ae6-632cc60e9b00}" ref="A1">
+    <comment authorId="1" xr:uid="{0c167707-c772-4a5c-8224-9ecfbe1f2637}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -203,7 +75,75 @@
 </t>
       </text>
     </comment>
-    <comment authorId="14" xr:uid="{aa5e53d1-26ac-4392-88ce-31414d0c5d3b}" ref="H26">
+    <comment authorId="2" xr:uid="{101a2eef-98f5-4e94-a791-55e3dc553754}" ref="I65">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Seems like it is public based on other uses of this data but the links don't work and I can't find a way to access it online...
+Reply:
+	Can't find it either, and it seems like the authors are from the same institution (Tel Aviv university) where the data came from, so I'd guess it's private?
+Also it's an fMRI dataset, which is outside our inclusion criteria, but we can include this in extra analysis
+</t>
+      </text>
+    </comment>
+    <comment authorId="3" xr:uid="{17326ac0-dbee-4866-bd9d-49536ff6670c}" ref="C7">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Same paper
+</t>
+      </text>
+    </comment>
+    <comment authorId="4" xr:uid="{1cb3283f-b2e6-4f63-8c45-5812449d6898}" ref="J4">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Age not mentioned for most datasets, except one with fetal gestational age
+</t>
+      </text>
+    </comment>
+    <comment authorId="5" xr:uid="{27924f17-c1d0-4d2f-b29d-b0790aafc430}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Adult/prenatal
+</t>
+      </text>
+    </comment>
+    <comment authorId="6" xr:uid="{2d2f55a4-bace-4147-9175-f4741b6542ef}" ref="H16">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	ATLAS v2.0 is used for testing. It's aggregated from other studies, and the age is unknown
+</t>
+      </text>
+    </comment>
+    <comment authorId="7" xr:uid="{33c636e8-f411-4087-b4c3-60e1bad5b313}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Waiting on approval
+</t>
+      </text>
+    </comment>
+    <comment authorId="8" xr:uid="{3b91a783-c71a-41a1-be39-c75e49de478d}" ref="F31">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	@stanley.z.hua@gmail.com Do you know if any of these have children?
+Reply:
+	Yes, CheXpert contains very little children! but it's unlikely that the COVID CXR dataset has any age annotation (so Unknown might be better? not sure)
+</t>
+      </text>
+    </comment>
+    <comment authorId="9" xr:uid="{4171f2a8-c9c8-48b6-b6f8-fcd776a3d527}" ref="H26">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -212,7 +152,97 @@
 </t>
       </text>
     </comment>
-    <comment authorId="15" xr:uid="{af370e31-5eca-4558-9048-99ee6d800e21}" ref="I67">
+    <comment authorId="10" xr:uid="{474565d4-43ba-449b-be22-266d57262e6d}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Revisit after getting access to paper
+</t>
+      </text>
+    </comment>
+    <comment authorId="11" xr:uid="{4c7ea26c-267f-4ae4-8c05-6de7fa405797}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Request was manually accepted a week later
+</t>
+      </text>
+    </comment>
+    <comment authorId="12" xr:uid="{62f45e37-0bce-43a8-892f-4c22e2b88192}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	So I think we should group "Research access" and "Public data" since a lot of these are actually research access but they are public in the sense that they are accessible for research?
+Reply:
+	Yeah, I think for our purposes/analyses, public and research data is the same
+1 total reaction
+Lauren Erdman reacted with 👍 at 2024-12-20 21:17 PM
+</t>
+      </text>
+    </comment>
+    <comment authorId="13" xr:uid="{82124f08-9139-4b66-8529-549d7747dcce}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	The ABIDE dataset contains pediatric patients
+</t>
+      </text>
+    </comment>
+    <comment authorId="14" xr:uid="{85357102-e5c2-44f9-92d4-04e51e318dbd}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Consider removing because of sample-size
+</t>
+      </text>
+    </comment>
+    <comment authorId="15" xr:uid="{9888ea57-0164-4785-823d-e7f82b2fb8d5}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Dataset-Level Metadata is used to estimate the proportion of datasets with age mentioned.
+Patient-Level Metadata is used to estimate the percentage of Peds vs. Adult data.
+Patient-Level Metadata (NeuroBagel): https://query.neurobagel.org/?node=OpenNeuro
+Dataset-Level Metadata: https://docs.google.com/spreadsheets/u/0/d/1rsVlKg0vBzkx7XUGK4joky9cM8umtkQRpJ2Y-5d6x7c/htmlview#
+</t>
+      </text>
+    </comment>
+    <comment authorId="16" xr:uid="{a28080ca-20e2-4398-a9c7-e8bd9944d043}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	MedSAM paper reports having 489 patients?
+</t>
+      </text>
+    </comment>
+    <comment authorId="17" xr:uid="{a450042a-5129-4cb8-9f19-4ff320540b5e}" ref="H13">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	@stanley.z.hua@gmail.com I can never remember or find if chexpert is adult only. Do you mind filling this in?
+Reply:
+	Done!
+</t>
+      </text>
+    </comment>
+    <comment authorId="18" xr:uid="{b6eab8f9-53cf-42cf-8c9e-62fb0cbee2dd}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	The UCLA dataset and ABIDE ASD dataset contain pediatric patients
+</t>
+      </text>
+    </comment>
+    <comment authorId="19" xr:uid="{c03a7816-4919-4fd0-b98e-97d48d832608}" ref="I67">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -223,57 +253,21 @@
 </t>
       </text>
     </comment>
-    <comment authorId="16" xr:uid="{b7fbe182-3cca-4c18-a3cf-50c0bc3b2646}" ref="A1">
+    <comment authorId="20" xr:uid="{d3327184-608f-4a96-bead-92b06806ba90}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Request was manually accepted a week later
+	Same paper as above
 </t>
       </text>
     </comment>
-    <comment authorId="17" xr:uid="{cb45dbb0-6787-444b-ae33-439c2583991f}" ref="A1">
+    <comment authorId="21" xr:uid="{da4efe22-4942-4752-9c86-b642520c0ab0}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	The UCLA dataset and ABIDE ASD dataset contain pediatric patients
-</t>
-      </text>
-    </comment>
-    <comment authorId="18" xr:uid="{d9d16971-1beb-4741-ba6b-b0d7ab144091}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Waiting on approval
-</t>
-      </text>
-    </comment>
-    <comment authorId="19" xr:uid="{e66f9bd8-27dc-437a-96bd-1e57ed80acda}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Adult/prenatal
-</t>
-      </text>
-    </comment>
-    <comment authorId="20" xr:uid="{ed3d849b-2462-40f9-9215-6a9636e6d22b}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Revisit after getting access to paper
-</t>
-      </text>
-    </comment>
-    <comment authorId="21" xr:uid="{efffed77-dbe3-45f6-a2a9-a0ff09cc82ef}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	MedSAM paper reports having 489 patients?
+	Awaiting review
 </t>
       </text>
     </comment>
@@ -284,10 +278,10 @@
 <file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={92bc1468-b0cd-4f56-a495-6872d9a9fc5e}</author>
+    <author>tc={bad3377f-f1fb-4d74-9e6d-4be6e49a0600}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{92bc1468-b0cd-4f56-a495-6872d9a9fc5e}" ref="A12">
+    <comment authorId="0" xr:uid="{bad3377f-f1fb-4d74-9e6d-4be6e49a0600}" ref="A12">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -303,10 +297,10 @@
 <file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={680d9e90-93e0-44db-a379-cf678d4756b3}</author>
+    <author>tc={4547c456-04b1-4a49-b36d-48f6b5f287c3}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{680d9e90-93e0-44db-a379-cf678d4756b3}" ref="N13">
+    <comment authorId="0" xr:uid="{4547c456-04b1-4a49-b36d-48f6b5f287c3}" ref="N13">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -322,25 +316,25 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={573dd1fb-eb63-40e4-aed0-8080da7c8360}</author>
-    <author>tc={8829f5c1-da18-4972-9437-1af493a12b88}</author>
+    <author>tc={4ec70f36-960e-4858-8e13-a02978838b3c}</author>
+    <author>tc={8f88ced7-0f86-47f1-822f-fd4e1a861590}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{573dd1fb-eb63-40e4-aed0-8080da7c8360}" ref="N19">
+    <comment authorId="0" xr:uid="{4ec70f36-960e-4858-8e13-a02978838b3c}" ref="N20">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Estimated from aggregated datasets with age information
+</t>
+      </text>
+    </comment>
+    <comment authorId="1" xr:uid="{8f88ced7-0f86-47f1-822f-fd4e1a861590}" ref="N19">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
 	The following are conservative estimates considering CheXpert and PadChest are the only datasets known to contain pediatric data (at &gt;99%)
-</t>
-      </text>
-    </comment>
-    <comment authorId="1" xr:uid="{8829f5c1-da18-4972-9437-1af493a12b88}" ref="N20">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Estimated from aggregated datasets with age information
 </t>
       </text>
     </comment>
@@ -351,14 +345,41 @@
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={489b7a54-7e8f-4a07-ae4a-b81e350e53df}</author>
-    <author>tc={49ca8b69-0d1e-4145-a1fe-71c606b35391}</author>
-    <author>tc={75d848da-ca67-405d-9959-505e1c1bcd74}</author>
-    <author>tc={79957c78-8358-4b4c-9666-3263808813c0}</author>
-    <author>tc={ef556ab6-e0f0-4773-b965-3c3de5b62761}</author>
+    <author>tc={3510f819-ecd7-4d4f-8ced-a943760ebc82}</author>
+    <author>tc={5b3d56a2-76a1-4bd8-98fd-4f57eb4ca479}</author>
+    <author>tc={8100ad5f-3f91-47ec-baee-268877255539}</author>
+    <author>tc={9bebaa40-ce34-4b3e-b138-827b7c23ea93}</author>
+    <author>tc={f635eee7-2ff4-403a-8c62-bd0a63f3140a}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{489b7a54-7e8f-4a07-ae4a-b81e350e53df}" ref="Q30">
+    <comment authorId="0" xr:uid="{3510f819-ecd7-4d4f-8ced-a943760ebc82}" ref="Q36">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Does not explicitly state that each sequence is a unique patient, but it should be
+</t>
+      </text>
+    </comment>
+    <comment authorId="1" xr:uid="{5b3d56a2-76a1-4bd8-98fd-4f57eb4ca479}" ref="G50">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Claims to have patient-level age annotation, but not available in the overview metadata (for each task) and in each nha file
+</t>
+      </text>
+    </comment>
+    <comment authorId="2" xr:uid="{8100ad5f-3f91-47ec-baee-268877255539}" ref="S22">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	For those with age information, only 1 patient identified to &lt; 18 years old (i.e., 14 years)
+</t>
+      </text>
+    </comment>
+    <comment authorId="3" xr:uid="{9bebaa40-ce34-4b3e-b138-827b7c23ea93}" ref="Q30">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -367,39 +388,12 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{49ca8b69-0d1e-4145-a1fe-71c606b35391}" ref="Q36">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Does not explicitly state that each sequence is a unique patient, but it should be
-</t>
-      </text>
-    </comment>
-    <comment authorId="2" xr:uid="{75d848da-ca67-405d-9959-505e1c1bcd74}" ref="G50">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Claims to have patient-level age annotation, but not available in the overview metadata (for each task) and in each nha file
-</t>
-      </text>
-    </comment>
-    <comment authorId="3" xr:uid="{79957c78-8358-4b4c-9666-3263808813c0}" ref="Q33">
+    <comment authorId="4" xr:uid="{f635eee7-2ff4-403a-8c62-bd0a63f3140a}" ref="Q33">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
 	Paper doesn't specify training/test split, so 4000 training images may be from less than 51 patients
-</t>
-      </text>
-    </comment>
-    <comment authorId="4" xr:uid="{ef556ab6-e0f0-4773-b965-3c3de5b62761}" ref="S22">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	For those with age information, only 1 patient identified to &lt; 18 years old (i.e., 14 years)
 </t>
       </text>
     </comment>
@@ -410,50 +404,15 @@
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={17b86f2e-263d-4169-a2f5-ed0779a8d0bc}</author>
-    <author>tc={1e570c19-a6f6-4dc4-bb0c-ce44d2b00afb}</author>
-    <author>tc={34c73520-0147-45f9-953e-6c2328a66899}</author>
-    <author>tc={836003d1-2c6f-4773-bb5f-aec1c6b2ec0e}</author>
-    <author>tc={99d984d3-5851-4119-ba7d-a67c3bd36e72}</author>
-    <author>tc={eb327126-4476-48b8-8fd6-79d650932b4b}</author>
+    <author>tc={06d9ecc6-a26a-47e9-b7c3-10f66edffca1}</author>
+    <author>tc={0977e7d1-2aa5-4a9b-89c5-d6303bc8d0b1}</author>
+    <author>tc={33677687-a7b1-4d10-bf0f-65e002b98b8f}</author>
+    <author>tc={4598e06d-be8d-435f-81fc-c41d6c9b3bff}</author>
+    <author>tc={9fb046b4-5758-466a-843f-d9437cae7237}</author>
+    <author>tc={f0f9173a-37d1-42a7-bce0-1ebb6487be30}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{17b86f2e-263d-4169-a2f5-ed0779a8d0bc}" ref="C8">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	https://pmc.ncbi.nlm.nih.gov/articles/PMC6367060/
-From 2005 to 2015
-Patients: 103
-Median Age: 68
-Age Range: 60 to 74
-Gender: M (47 patients), F (56 patients)
-https://pmc.ncbi.nlm.nih.gov/articles/PMC6752719/
-From 2009 to 2012
-Patients: 161
-Sex: M (82 patients), F (79 patients)
-Median Age: 67
-Age Range: 58 to 79
-https://pmc.ncbi.nlm.nih.gov/articles/PMC8050835/
-From 2005 to 2015
-Patients: 103
-Median Age: 68
-Age Range: 44 to 90
-Gender: M (47 patients), F (56 patients)
-</t>
-      </text>
-    </comment>
-    <comment authorId="1" xr:uid="{1e570c19-a6f6-4dc4-bb0c-ce44d2b00afb}" ref="A13">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Fitzpatrick17k and HAM1000 have been excluded due to imaging inclusion criteria
-</t>
-      </text>
-    </comment>
-    <comment authorId="2" xr:uid="{34c73520-0147-45f9-953e-6c2328a66899}" ref="N2">
+    <comment authorId="0" xr:uid="{06d9ecc6-a26a-47e9-b7c3-10f66edffca1}" ref="N2">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -462,25 +421,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="3" xr:uid="{836003d1-2c6f-4773-bb5f-aec1c6b2ec0e}" ref="N3">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Can be inferred to be adult based on focus on left ventricle
-</t>
-      </text>
-    </comment>
-    <comment authorId="4" xr:uid="{99d984d3-5851-4119-ba7d-a67c3bd36e72}" ref="N15">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	2 of 244 patients are in the age range 14 to 24
-</t>
-      </text>
-    </comment>
-    <comment authorId="5" xr:uid="{eb327126-4476-48b8-8fd6-79d650932b4b}" ref="C9">
+    <comment authorId="1" xr:uid="{0977e7d1-2aa5-4a9b-89c5-d6303bc8d0b1}" ref="C9">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -508,6 +449,59 @@
 </t>
       </text>
     </comment>
+    <comment authorId="2" xr:uid="{33677687-a7b1-4d10-bf0f-65e002b98b8f}" ref="N3">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Can be inferred to be adult based on focus on left ventricle
+</t>
+      </text>
+    </comment>
+    <comment authorId="3" xr:uid="{4598e06d-be8d-435f-81fc-c41d6c9b3bff}" ref="A13">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Fitzpatrick17k and HAM1000 have been excluded due to imaging inclusion criteria
+</t>
+      </text>
+    </comment>
+    <comment authorId="4" xr:uid="{9fb046b4-5758-466a-843f-d9437cae7237}" ref="N15">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	2 of 244 patients are in the age range 14 to 24
+</t>
+      </text>
+    </comment>
+    <comment authorId="5" xr:uid="{f0f9173a-37d1-42a7-bce0-1ebb6487be30}" ref="C8">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	https://pmc.ncbi.nlm.nih.gov/articles/PMC6367060/
+From 2005 to 2015
+Patients: 103
+Median Age: 68
+Age Range: 60 to 74
+Gender: M (47 patients), F (56 patients)
+https://pmc.ncbi.nlm.nih.gov/articles/PMC6752719/
+From 2009 to 2012
+Patients: 161
+Sex: M (82 patients), F (79 patients)
+Median Age: 67
+Age Range: 58 to 79
+https://pmc.ncbi.nlm.nih.gov/articles/PMC8050835/
+From 2005 to 2015
+Patients: 103
+Median Age: 68
+Age Range: 44 to 90
+Gender: M (47 patients), F (56 patients)
+</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -515,16 +509,25 @@
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={092211c5-9df5-48e6-a654-e0ae7edc239c}</author>
-    <author>tc={3bdbc492-fbd7-4a41-997a-2b7528574523}</author>
-    <author>tc={6d8c1669-94e5-4148-8651-8e006fdf0643}</author>
-    <author>tc={6f26d3ac-ee71-4f11-bf07-33edb05df08d}</author>
-    <author>tc={80cc4ac8-b5c9-468f-b39a-aea57aeab627}</author>
-    <author>tc={b3d79dc2-a9c3-48b7-8313-7b4359321316}</author>
-    <author>tc={fbb991a1-3dbd-4a4b-9a30-b219bafcfb26}</author>
+    <author>tc={1e22a16e-ff77-4c82-9d37-778797064efc}</author>
+    <author>tc={217ebd8d-2dfb-401e-8155-78c5cb9c7067}</author>
+    <author>tc={47339414-6e09-47b5-a115-cdd65b3dc56d}</author>
+    <author>tc={5cd4cb81-4718-4606-b17c-c991d4b32a4f}</author>
+    <author>tc={62846516-f02f-4f93-a3c5-ccbb741a9126}</author>
+    <author>tc={91fcb9c7-cd6b-4e3a-99e5-29bd415d595e}</author>
+    <author>tc={f0134036-e81d-4f8c-832c-47e5fa6b14ca}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{092211c5-9df5-48e6-a654-e0ae7edc239c}" ref="D16">
+    <comment authorId="0" xr:uid="{1e22a16e-ff77-4c82-9d37-778797064efc}" ref="O19">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Inferred
+</t>
+      </text>
+    </comment>
+    <comment authorId="1" xr:uid="{217ebd8d-2dfb-401e-8155-78c5cb9c7067}" ref="D16">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -533,7 +536,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{3bdbc492-fbd7-4a41-997a-2b7528574523}" ref="O6">
+    <comment authorId="2" xr:uid="{47339414-6e09-47b5-a115-cdd65b3dc56d}" ref="O6">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -542,16 +545,25 @@
 </t>
       </text>
     </comment>
-    <comment authorId="2" xr:uid="{6d8c1669-94e5-4148-8651-8e006fdf0643}" ref="O19">
+    <comment authorId="3" xr:uid="{5cd4cb81-4718-4606-b17c-c991d4b32a4f}" ref="O20">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Inferred
+	Likely adult
 </t>
       </text>
     </comment>
-    <comment authorId="3" xr:uid="{6f26d3ac-ee71-4f11-bf07-33edb05df08d}" ref="O12">
+    <comment authorId="4" xr:uid="{62846516-f02f-4f93-a3c5-ccbb741a9126}" ref="O11">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Can be estimated to be Adult (&gt;84%) based on unknown presence of peds data
+</t>
+      </text>
+    </comment>
+    <comment authorId="5" xr:uid="{91fcb9c7-cd6b-4e3a-99e5-29bd415d595e}" ref="O12">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -560,30 +572,12 @@
 </t>
       </text>
     </comment>
-    <comment authorId="4" xr:uid="{80cc4ac8-b5c9-468f-b39a-aea57aeab627}" ref="O11">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Can be estimated to be Adult (&gt;84%) based on unknown presence of peds data
-</t>
-      </text>
-    </comment>
-    <comment authorId="5" xr:uid="{b3d79dc2-a9c3-48b7-8313-7b4359321316}" ref="A17">
+    <comment authorId="6" xr:uid="{f0134036-e81d-4f8c-832c-47e5fa6b14ca}" ref="A17">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
 	Paper mentions how morphology of retina of infants and children are different from adults
-</t>
-      </text>
-    </comment>
-    <comment authorId="6" xr:uid="{fbb991a1-3dbd-4a4b-9a30-b219bafcfb26}" ref="O20">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Likely adult
 </t>
       </text>
     </comment>
@@ -594,11 +588,11 @@
 <file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={19b86709-d503-43ac-a9a3-18aa966a647f}</author>
-    <author>tc={26c0d354-cb26-4a29-8bae-0dd9e624c31c}</author>
+    <author>tc={0dc8e530-8f38-4506-ba7b-de0f5bc846fd}</author>
+    <author>tc={a69256dd-14fb-4be7-8b98-cd2618432383}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{19b86709-d503-43ac-a9a3-18aa966a647f}" ref="A2">
+    <comment authorId="0" xr:uid="{0dc8e530-8f38-4506-ba7b-de0f5bc846fd}" ref="A2">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -609,7 +603,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{26c0d354-cb26-4a29-8bae-0dd9e624c31c}" ref="A3">
+    <comment authorId="1" xr:uid="{a69256dd-14fb-4be7-8b98-cd2618432383}" ref="A3">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -632,10 +626,10 @@
 <file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={f342eddf-cc07-448b-b1cb-bcadaf6e28d3}</author>
+    <author>tc={161a12f3-f5e1-4b99-a183-957c9e3bc745}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{f342eddf-cc07-448b-b1cb-bcadaf6e28d3}" ref="A2">
+    <comment authorId="0" xr:uid="{161a12f3-f5e1-4b99-a183-957c9e3bc745}" ref="A2">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -653,11 +647,20 @@
 <file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={6135d8d7-ba59-4340-8cb2-a11766444adf}</author>
-    <author>tc={e85e7a11-0851-4ff7-ae24-c893a17606f7}</author>
+    <author>tc={3226d114-5263-4065-93c9-d9c800478e26}</author>
+    <author>tc={4af21bd8-0f21-4a21-bf50-fbcc86efdca4}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{6135d8d7-ba59-4340-8cb2-a11766444adf}" ref="A2">
+    <comment authorId="0" xr:uid="{3226d114-5263-4065-93c9-d9c800478e26}" ref="M43">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Estimated from description. Since each patient has 1 pre-treatment and at most 1 follow-up
+</t>
+      </text>
+    </comment>
+    <comment authorId="1" xr:uid="{4af21bd8-0f21-4a21-bf50-fbcc86efdca4}" ref="A2">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -672,15 +675,6 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{e85e7a11-0851-4ff7-ae24-c893a17606f7}" ref="M43">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Estimated from description. Since each patient has 1 pre-treatment and at most 1 follow-up
-</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -688,25 +682,25 @@
 <file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={4ab1f9cd-9bab-4f57-814b-27e7f7ab1a1b}</author>
-    <author>tc={6d4a8d56-2df8-488e-9211-8614a6873217}</author>
+    <author>tc={28aa5bc6-a9d2-430c-872b-fbeedf5c1a12}</author>
+    <author>tc={29567dbc-be14-4a52-b8f9-296c952a6c8d}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{4ab1f9cd-9bab-4f57-814b-27e7f7ab1a1b}" ref="R15">
+    <comment authorId="0" xr:uid="{28aa5bc6-a9d2-430c-872b-fbeedf5c1a12}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	2021 QUBIQ challenge was excluded because it didn't specify source of secondary datasets
+</t>
+      </text>
+    </comment>
+    <comment authorId="1" xr:uid="{29567dbc-be14-4a52-b8f9-296c952a6c8d}" ref="R15">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
 	This was manually curated. See Repackaging (VQA-RAD) tab
-</t>
-      </text>
-    </comment>
-    <comment authorId="1" xr:uid="{6d4a8d56-2df8-488e-9211-8614a6873217}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	2021 QUBIQ challenge was excluded because it didn't specify source of secondary datasets
 </t>
       </text>
     </comment>
@@ -15099,22 +15093,22 @@
 
 <file path=xl/documenttasks/documenttask1.xml><?xml version="1.0" encoding="utf-8"?>
 <Tasks xmlns="http://schemas.microsoft.com/office/tasks/2019/documenttasks">
-  <Task id="{51a0b661-6a25-468c-81cd-4150659379c3}">
+  <Task id="{f3f4da86-a460-4390-8cab-5d0f428ac0a6}">
     <Anchor>
-      <Comment id="{a24a3e3f-c726-441a-8ae6-632cc60e9b00}"/>
+      <Comment id="{0c167707-c772-4a5c-8224-9ecfbe1f2637}"/>
     </Anchor>
     <History>
-      <Event time="2024-11-22T04:23:57.00" id="{0896600d-d3ff-4c4e-b14c-7f9cd68f9716}">
+      <Event time="2024-11-22T04:23:57.00" id="{6357db3e-6400-4c50-850e-177de923e3ef}">
         <Attribution userId="placeholder@email.com" userName="Lauren Erdman" userProvider="google-sheets"/>
         <Anchor>
-          <Comment id="{a24a3e3f-c726-441a-8ae6-632cc60e9b00}"/>
+          <Comment id="{0c167707-c772-4a5c-8224-9ecfbe1f2637}"/>
         </Anchor>
         <Create/>
       </Event>
-      <Event time="2024-11-22T04:23:57.00" id="{23f823d0-1fe2-464c-b914-da2d6dd092e1}">
+      <Event time="2024-11-22T04:23:57.00" id="{b04070ea-7f9e-412b-bdf0-ba24e315a970}">
         <Attribution userId="placeholder@email.com" userName="Lauren Erdman" userProvider="google-sheets"/>
         <Anchor>
-          <Comment id="{a24a3e3f-c726-441a-8ae6-632cc60e9b00}"/>
+          <Comment id="{0c167707-c772-4a5c-8224-9ecfbe1f2637}"/>
         </Anchor>
         <Assign userId="stanley.z.hua@gmail.com" userName="stanley.z.hua@gmail.com" userProvider="google-sheets"/>
       </Event>
@@ -15225,10 +15219,10 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Stanley Hua" id="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" providerId="google-sheets"/>
-  <x18tc:person displayName="Lauren Erdman" id="{9b426865-153d-45dd-9ab1-66ee3ba6cf77}" providerId="google-sheets"/>
-  <x18tc:person displayName="Stanley Hua" id="{e7da1d36-66dd-44ad-afd2-ea4a46adf9eb}" providerId="google-sheets"/>
-  <x18tc:person displayName="stanley.z.hua@gmail.com" id="{fb3a89ff-6f99-4217-9d39-6c9de2426c78}" userId="stanley.z.hua@gmail.com" providerId="google-sheets"/>
+  <x18tc:person displayName="stanley.z.hua@gmail.com" id="{4f9554a0-c707-4317-bcad-f5573cc17d4b}" userId="stanley.z.hua@gmail.com" providerId="google-sheets"/>
+  <x18tc:person displayName="Lauren Erdman" id="{26617188-0fe7-4f5a-9e79-0143f6ca1d5a}" providerId="google-sheets"/>
+  <x18tc:person displayName="Stanley Hua" id="{7f9de00e-c95a-4553-a00e-5510805f5b06}" providerId="google-sheets"/>
+  <x18tc:person displayName="Stanley Hua" id="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -15283,13 +15277,6 @@
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:P27" displayName="Table1_3" name="Table1_3" id="11">
-  <autoFilter ref="$A$1:$P$27">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="Patient-Level"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <tableColumns count="16">
     <tableColumn name="Dataset Name" id="1"/>
     <tableColumn name="Link" id="2"/>
@@ -15429,7 +15416,6 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:X59" displayName="Table_1" name="Table_1" id="3">
-  <autoFilter ref="$A$1:$X$59"/>
   <tableColumns count="24">
     <tableColumn name="Dataset Name" id="1"/>
     <tableColumn name="Link" id="2"/>
@@ -15489,13 +15475,6 @@
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:Z31" displayName="Table_1_5" name="Table_1_5" id="5">
-  <autoFilter ref="$A$1:$Z$31">
-    <filterColumn colId="13">
-      <filters>
-        <filter val="US"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <tableColumns count="26">
     <tableColumn name="Dataset Name" id="1"/>
     <tableColumn name="Also In" id="2"/>
@@ -15556,13 +15535,6 @@
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:S14" displayName="Table_1_9" name="Table_1_9" id="7">
-  <autoFilter ref="$A$1:$S$14">
-    <filterColumn colId="13">
-      <filters>
-        <filter val="US"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <tableColumns count="19">
     <tableColumn name="Image Collection" id="1"/>
     <tableColumn name="Dataset Name" id="2"/>
@@ -15617,7 +15589,6 @@
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:K25" displayName="Table4" name="Table4" id="9">
-  <autoFilter ref="$A$1:$K$25"/>
   <tableColumns count="11">
     <tableColumn name="Image Collection" id="1"/>
     <tableColumn name="Dataset Name" id="2"/>
@@ -15831,80 +15802,80 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="A1" dT="2024-11-28T20:26:52.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{86244669-eb33-4030-975e-5bfdeaf87de5}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2024-11-28T20:26:52.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{82124f08-9139-4b66-8529-549d7747dcce}" done="0">
     <x18tc:text xml:space="preserve">The ABIDE dataset contains pediatric patients</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2024-10-10T20:18:25.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{15d0c6b0-d221-41d9-a5ef-8b7f2fc1ae45}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2024-10-10T20:18:25.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{da4efe22-4942-4752-9c86-b642520c0ab0}" done="0">
     <x18tc:text xml:space="preserve">Awaiting review</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="H26" dT="2024-12-10T22:02:30.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{aa5e53d1-26ac-4392-88ce-31414d0c5d3b}" done="1">
+  <x18tc:threadedComment ref="H26" dT="2024-12-10T22:02:30.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{4171f2a8-c9c8-48b6-b6f8-fcd776a3d527}" done="1">
     <x18tc:text xml:space="preserve">Inclusion criteria includes &gt;= 18 years</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="H16" dT="2024-12-10T21:51:37.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{77fce280-284f-4d10-bfe6-e9b0c082d4a1}" done="1">
+  <x18tc:threadedComment ref="H16" dT="2024-12-10T21:51:37.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{2d2f55a4-bace-4147-9175-f4741b6542ef}" done="1">
     <x18tc:text xml:space="preserve">ATLAS v2.0 is used for testing. It's aggregated from other studies, and the age is unknown</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F31" dT="2024-12-19T23:12:55.00" personId="{9b426865-153d-45dd-9ab1-66ee3ba6cf77}" id="{81dc5f9c-873d-485a-9f36-f9d6447bdaa4}" done="1">
+  <x18tc:threadedComment ref="F31" dT="2024-12-19T23:12:55.00" personId="{26617188-0fe7-4f5a-9e79-0143f6ca1d5a}" id="{3b91a783-c71a-41a1-be39-c75e49de478d}" done="1">
     <x18tc:text xml:space="preserve">@stanley.z.hua@gmail.com Do you know if any of these have children?</x18tc:text>
     <x18tc:mentions>
-      <x18tc:mention mentionpersonId="{fb3a89ff-6f99-4217-9d39-6c9de2426c78}" mentionId="{505f8280-ef49-4dc6-93b8-4e95d486f7ba}" startIndex="0" length="24"/>
+      <x18tc:mention mentionpersonId="{4f9554a0-c707-4317-bcad-f5573cc17d4b}" mentionId="{68c4268b-fd94-4fc0-baf3-5547fa8ca746}" startIndex="0" length="24"/>
     </x18tc:mentions>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F31" dT="2024-12-20T18:57:34.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{ad881114-5123-4c03-8e85-a14162a4d72a}" parentId="{81dc5f9c-873d-485a-9f36-f9d6447bdaa4}">
+  <x18tc:threadedComment ref="F31" dT="2024-12-20T18:57:34.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{8200976a-52e7-498a-8821-257440f07bb1}" parentId="{3b91a783-c71a-41a1-be39-c75e49de478d}">
     <x18tc:text xml:space="preserve">Yes, CheXpert contains very little children! but it's unlikely that the COVID CXR dataset has any age annotation (so Unknown might be better? not sure)</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="C7" dT="2024-12-20T21:19:52.00" personId="{9b426865-153d-45dd-9ab1-66ee3ba6cf77}" id="{929cb761-c6e6-4b7b-96d7-9199a3702c2f}" done="1">
+  <x18tc:threadedComment ref="C7" dT="2024-12-20T21:19:52.00" personId="{26617188-0fe7-4f5a-9e79-0143f6ca1d5a}" id="{17326ac0-dbee-4866-bd9d-49536ff6670c}" done="1">
     <x18tc:text xml:space="preserve">Same paper</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2024-11-19T20:13:33.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{8b1ec243-3d92-4415-af7f-b2154f4f6ecb}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2024-11-19T20:13:33.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{000797c7-a047-48f0-b911-83900582991f}" done="0">
     <x18tc:text xml:space="preserve">If filtering for TCIA datasets with demographics, then this should be removed</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2024-12-19T23:48:02.00" personId="{9b426865-153d-45dd-9ab1-66ee3ba6cf77}" id="{18f530a5-07e4-4904-9737-70895410aa30}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2024-12-19T23:48:02.00" personId="{26617188-0fe7-4f5a-9e79-0143f6ca1d5a}" id="{62f45e37-0bce-43a8-892f-4c22e2b88192}" done="0">
     <x18tc:text xml:space="preserve">So I think we should group "Research access" and "Public data" since a lot of these are actually research access but they are public in the sense that they are accessible for research?</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2024-12-20T18:58:10.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{b099c5de-dcfc-4a6c-9806-200c15e4baf3}" parentId="{18f530a5-07e4-4904-9737-70895410aa30}">
+  <x18tc:threadedComment ref="A1" dT="2024-12-20T18:58:10.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{cf14c699-a197-4645-863a-041b1104655c}" parentId="{62f45e37-0bce-43a8-892f-4c22e2b88192}">
     <x18tc:text xml:space="preserve">Yeah, I think for our purposes/analyses, public and research data is the same
 1 total reaction
 Lauren Erdman reacted with 👍 at 2024-12-20 21:17 PM</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2024-10-10T18:32:50.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{d9d16971-1beb-4741-ba6b-b0d7ab144091}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2024-10-10T18:32:50.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{33c636e8-f411-4087-b4c3-60e1bad5b313}" done="0">
     <x18tc:text xml:space="preserve">Waiting on approval</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="I65" dT="2024-12-20T00:15:41.00" personId="{9b426865-153d-45dd-9ab1-66ee3ba6cf77}" id="{79d54332-c935-4812-bf26-25afe4416f4e}" done="0">
+  <x18tc:threadedComment ref="I65" dT="2024-12-20T00:15:41.00" personId="{26617188-0fe7-4f5a-9e79-0143f6ca1d5a}" id="{101a2eef-98f5-4e94-a791-55e3dc553754}" done="0">
     <x18tc:text xml:space="preserve">Seems like it is public based on other uses of this data but the links don't work and I can't find a way to access it online...</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="I65" dT="2024-12-24T16:02:00.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{dd8e210a-5827-4d48-9982-0cf5c7230929}" parentId="{79d54332-c935-4812-bf26-25afe4416f4e}">
+  <x18tc:threadedComment ref="I65" dT="2024-12-24T16:02:00.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{5f71259e-5def-47fd-985c-da110a5ccf2c}" parentId="{101a2eef-98f5-4e94-a791-55e3dc553754}">
     <x18tc:text xml:space="preserve">Can't find it either, and it seems like the authors are from the same institution (Tel Aviv university) where the data came from, so I'd guess it's private?
 Also it's an fMRI dataset, which is outside our inclusion criteria, but we can include this in extra analysis</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2024-12-19T15:36:21.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{6aa35232-dc3e-4fc3-88a9-b16de6dee409}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2024-12-19T15:36:21.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{85357102-e5c2-44f9-92d4-04e51e318dbd}" done="0">
     <x18tc:text xml:space="preserve">Consider removing because of sample-size</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="H13" dT="2024-12-18T16:14:23.00" personId="{9b426865-153d-45dd-9ab1-66ee3ba6cf77}" id="{30657624-dd6e-49e4-bbc4-9105cbd1ff54}" done="1">
+  <x18tc:threadedComment ref="H13" dT="2024-12-18T16:14:23.00" personId="{26617188-0fe7-4f5a-9e79-0143f6ca1d5a}" id="{a450042a-5129-4cb8-9f19-4ff320540b5e}" done="1">
     <x18tc:text xml:space="preserve">@stanley.z.hua@gmail.com I can never remember or find if chexpert is adult only. Do you mind filling this in?</x18tc:text>
     <x18tc:mentions>
-      <x18tc:mention mentionpersonId="{fb3a89ff-6f99-4217-9d39-6c9de2426c78}" mentionId="{274b78a8-3c3c-4713-88bd-80d67fbebb61}" startIndex="0" length="24"/>
+      <x18tc:mention mentionpersonId="{4f9554a0-c707-4317-bcad-f5573cc17d4b}" mentionId="{e4a1203f-552e-432c-9167-eadae9781c9d}" startIndex="0" length="24"/>
     </x18tc:mentions>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="H13" dT="2024-12-19T20:02:16.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{0ed92fc7-7033-4cec-ab78-e824ba4df263}" parentId="{30657624-dd6e-49e4-bbc4-9105cbd1ff54}">
+  <x18tc:threadedComment ref="H13" dT="2024-12-19T20:02:16.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{08751abb-fcb8-4fa2-98c9-48de0e55d30a}" parentId="{a450042a-5129-4cb8-9f19-4ff320540b5e}">
     <x18tc:text xml:space="preserve">Done!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2024-10-17T15:47:51.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{b7fbe182-3cca-4c18-a3cf-50c0bc3b2646}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2024-10-17T15:47:51.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{4c7ea26c-267f-4ae4-8c05-6de7fa405797}" done="0">
     <x18tc:text xml:space="preserve">Request was manually accepted a week later</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="I67" dT="2024-12-20T01:13:44.00" personId="{9b426865-153d-45dd-9ab1-66ee3ba6cf77}" id="{af370e31-5eca-4558-9048-99ee6d800e21}" done="0">
+  <x18tc:threadedComment ref="I67" dT="2024-12-20T01:13:44.00" personId="{26617188-0fe7-4f5a-9e79-0143f6ca1d5a}" id="{c03a7816-4919-4fd0-b98e-97d48d832608}" done="0">
     <x18tc:text xml:space="preserve">The data is named as if it is public but I cannot find it anywhere...</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="I67" dT="2024-12-24T16:03:31.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{0981903a-904b-43ef-8257-68ba3ff45c85}" parentId="{af370e31-5eca-4558-9048-99ee6d800e21}">
+  <x18tc:threadedComment ref="I67" dT="2024-12-24T16:03:31.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{20e53364-dce1-4fcd-94f2-6f153ffe07d6}" parentId="{c03a7816-4919-4fd0-b98e-97d48d832608}">
     <x18tc:text xml:space="preserve">Yeah it's definitely private for now, probably named for convenience</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2024-11-28T20:26:39.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{cb45dbb0-6787-444b-ae33-439c2583991f}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2024-11-28T20:26:39.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{b6eab8f9-53cf-42cf-8c9e-62fb0cbee2dd}" done="0">
     <x18tc:text xml:space="preserve">The UCLA dataset and ABIDE ASD dataset contain pediatric patients</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2024-11-22T04:23:57.00" personId="{9b426865-153d-45dd-9ab1-66ee3ba6cf77}" id="{a24a3e3f-c726-441a-8ae6-632cc60e9b00}" done="1">
+  <x18tc:threadedComment ref="A1" dT="2024-11-22T04:23:57.00" personId="{26617188-0fe7-4f5a-9e79-0143f6ca1d5a}" id="{0c167707-c772-4a5c-8224-9ecfbe1f2637}" done="1">
     <x18tc:text xml:space="preserve">@stanley.z.hua@gmail.com Can you check out the datasets here and see if you recognize any as having peds data or if you've already shown they're all adult? If not, feel free to keep it as unknown! https://www.mdpi.com/2076-3417/11/2/672
 Assigned to stanley.z.hua@gmail.com</x18tc:text>
     <x18tc:mentions>
-      <x18tc:mention mentionpersonId="{fb3a89ff-6f99-4217-9d39-6c9de2426c78}" mentionId="{8e3bec44-fa34-455b-a60f-35bf72e0b007}" startIndex="0" length="24"/>
+      <x18tc:mention mentionpersonId="{4f9554a0-c707-4317-bcad-f5573cc17d4b}" mentionId="{a8c65d01-1d79-442d-bce5-97fe83ada378}" startIndex="0" length="24"/>
     </x18tc:mentions>
     <x18tc:extLst>
       <ext uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -15913,25 +15884,25 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2024-11-22T17:51:50.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{8669ecfc-5678-4db8-b841-616923273a81}" parentId="{a24a3e3f-c726-441a-8ae6-632cc60e9b00}">
+  <x18tc:threadedComment ref="A1" dT="2024-11-22T17:51:50.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{f97b7780-a122-4db3-89ce-2e90a7297248}" parentId="{0c167707-c772-4a5c-8224-9ecfbe1f2637}">
     <x18tc:text xml:space="preserve">I'm actually using this dataset for the OOD ultrasound project too lol
 Just checked, but for the known 70%, they're all adults. We can mark it as Adult Only, but just need to write that somewhere
 1 total reaction
 Lauren Erdman reacted with 👌 at 2024-11-28 18:54 PM</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2025-11-04T05:11:34.00" personId="{e7da1d36-66dd-44ad-afd2-ea4a46adf9eb}" id="{efffed77-dbe3-45f6-a2a9-a0ff09cc82ef}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2025-11-04T05:11:34.00" personId="{7f9de00e-c95a-4553-a00e-5510805f5b06}" id="{a28080ca-20e2-4398-a9c7-e8bd9944d043}" done="0">
     <x18tc:text xml:space="preserve">MedSAM paper reports having 489 patients?</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2024-10-08T14:13:10.00" personId="{9b426865-153d-45dd-9ab1-66ee3ba6cf77}" id="{e66f9bd8-27dc-437a-96bd-1e57ed80acda}" done="1">
+  <x18tc:threadedComment ref="A1" dT="2024-10-08T14:13:10.00" personId="{26617188-0fe7-4f5a-9e79-0143f6ca1d5a}" id="{27924f17-c1d0-4d2f-b29d-b0790aafc430}" done="1">
     <x18tc:text xml:space="preserve">Adult/prenatal</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2024-09-13T21:09:59.00" personId="{e7da1d36-66dd-44ad-afd2-ea4a46adf9eb}" id="{ed3d849b-2462-40f9-9215-6a9636e6d22b}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2024-09-13T21:09:59.00" personId="{7f9de00e-c95a-4553-a00e-5510805f5b06}" id="{474565d4-43ba-449b-be22-266d57262e6d}" done="0">
     <x18tc:text xml:space="preserve">Revisit after getting access to paper</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="J4" dT="2024-12-25T18:51:19.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{68402715-6c3d-4a13-a4cf-fc05c4c49e47}" done="0">
+  <x18tc:threadedComment ref="J4" dT="2024-12-25T18:51:19.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{1cb3283f-b2e6-4f63-8c45-5812449d6898}" done="0">
     <x18tc:text xml:space="preserve">Age not mentioned for most datasets, except one with fetal gestational age</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2024-12-23T18:11:27.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{880f0d25-4437-4265-afa4-de1d229c0ad5}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2024-12-23T18:11:27.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{9888ea57-0164-4785-823d-e7f82b2fb8d5}" done="0">
     <x18tc:text xml:space="preserve">Dataset-Level Metadata is used to estimate the proportion of datasets with age mentioned.
 Patient-Level Metadata is used to estimate the percentage of Peds vs. Adult data.
 Patient-Level Metadata (NeuroBagel): https://query.neurobagel.org/?node=OpenNeuro
@@ -15944,7 +15915,7 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2024-12-19T20:05:34.00" personId="{9b426865-153d-45dd-9ab1-66ee3ba6cf77}" id="{580d2974-de9e-43ff-8fa9-81c3e9fd3ae6}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2024-12-19T20:05:34.00" personId="{26617188-0fe7-4f5a-9e79-0143f6ca1d5a}" id="{d3327184-608f-4a96-bead-92b06806ba90}" done="0">
     <x18tc:text xml:space="preserve">Same paper as above</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -15952,7 +15923,7 @@
 
 <file path=xl/threadedComments/threadedComment10.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="A12" dT="2025-03-17T14:23:50.00" personId="{e7da1d36-66dd-44ad-afd2-ea4a46adf9eb}" id="{92bc1468-b0cd-4f56-a495-6872d9a9fc5e}" done="0">
+  <x18tc:threadedComment ref="A12" dT="2025-03-17T14:23:50.00" personId="{7f9de00e-c95a-4553-a00e-5510805f5b06}" id="{bad3377f-f1fb-4d74-9e6d-4be6e49a0600}" done="0">
     <x18tc:text xml:space="preserve">This is not referenced among the Primary datasets, but is kept here to compare with KiTS19/21</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -15960,7 +15931,7 @@
 
 <file path=xl/threadedComments/threadedComment11.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="N13" dT="2025-11-04T05:16:30.00" personId="{e7da1d36-66dd-44ad-afd2-ea4a46adf9eb}" id="{680d9e90-93e0-44db-a379-cf678d4756b3}" done="0">
+  <x18tc:threadedComment ref="N13" dT="2025-11-04T05:16:30.00" personId="{7f9de00e-c95a-4553-a00e-5510805f5b06}" id="{4547c456-04b1-4a49-b36d-48f6b5f287c3}" done="0">
     <x18tc:text xml:space="preserve">MedSAM reports 489</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -15968,10 +15939,10 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="N19" dT="2025-01-24T20:23:22.00" personId="{e7da1d36-66dd-44ad-afd2-ea4a46adf9eb}" id="{573dd1fb-eb63-40e4-aed0-8080da7c8360}" done="1">
+  <x18tc:threadedComment ref="N19" dT="2025-01-24T20:23:22.00" personId="{7f9de00e-c95a-4553-a00e-5510805f5b06}" id="{8f88ced7-0f86-47f1-822f-fd4e1a861590}" done="1">
     <x18tc:text xml:space="preserve">The following are conservative estimates considering CheXpert and PadChest are the only datasets known to contain pediatric data (at &gt;99%)</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="N20" dT="2025-05-21T14:21:10.00" personId="{e7da1d36-66dd-44ad-afd2-ea4a46adf9eb}" id="{8829f5c1-da18-4972-9437-1af493a12b88}" done="1">
+  <x18tc:threadedComment ref="N20" dT="2025-05-21T14:21:10.00" personId="{7f9de00e-c95a-4553-a00e-5510805f5b06}" id="{4ec70f36-960e-4858-8e13-a02978838b3c}" done="1">
     <x18tc:text xml:space="preserve">Estimated from aggregated datasets with age information</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -15979,19 +15950,19 @@
 
 <file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="Q36" dT="2024-10-10T20:27:57.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{49ca8b69-0d1e-4145-a1fe-71c606b35391}" done="1">
+  <x18tc:threadedComment ref="Q36" dT="2024-10-10T20:27:57.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{3510f819-ecd7-4d4f-8ced-a943760ebc82}" done="1">
     <x18tc:text xml:space="preserve">Does not explicitly state that each sequence is a unique patient, but it should be</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="S22" dT="2024-10-10T18:43:32.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{ef556ab6-e0f0-4773-b965-3c3de5b62761}" done="1">
+  <x18tc:threadedComment ref="S22" dT="2024-10-10T18:43:32.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{8100ad5f-3f91-47ec-baee-268877255539}" done="1">
     <x18tc:text xml:space="preserve">For those with age information, only 1 patient identified to &lt; 18 years old (i.e., 14 years)</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="Q30" dT="2024-10-10T18:18:31.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{489b7a54-7e8f-4a07-ae4a-b81e350e53df}" done="1">
+  <x18tc:threadedComment ref="Q30" dT="2024-10-10T18:18:31.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{9bebaa40-ce34-4b3e-b138-827b7c23ea93}" done="1">
     <x18tc:text xml:space="preserve">Includes validation images without labels/annotations</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="Q33" dT="2024-10-10T19:56:30.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{79957c78-8358-4b4c-9666-3263808813c0}" done="1">
+  <x18tc:threadedComment ref="Q33" dT="2024-10-10T19:56:30.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{f635eee7-2ff4-403a-8c62-bd0a63f3140a}" done="1">
     <x18tc:text xml:space="preserve">Paper doesn't specify training/test split, so 4000 training images may be from less than 51 patients</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="G50" dT="2024-12-16T20:15:02.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{75d848da-ca67-405d-9959-505e1c1bcd74}" done="0">
+  <x18tc:threadedComment ref="G50" dT="2024-12-16T20:15:02.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{5b3d56a2-76a1-4bd8-98fd-4f57eb4ca479}" done="0">
     <x18tc:text xml:space="preserve">Claims to have patient-level age annotation, but not available in the overview metadata (for each task) and in each nha file</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -15999,19 +15970,19 @@
 
 <file path=xl/threadedComments/threadedComment4.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="N2" dT="2024-11-04T16:14:06.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{34c73520-0147-45f9-953e-6c2328a66899}" done="1">
+  <x18tc:threadedComment ref="N2" dT="2024-11-04T16:14:06.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{06d9ecc6-a26a-47e9-b7c3-10f66edffca1}" done="1">
     <x18tc:text xml:space="preserve">Inferred</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="N15" dT="2024-11-12T19:24:11.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{99d984d3-5851-4119-ba7d-a67c3bd36e72}" done="0">
+  <x18tc:threadedComment ref="N15" dT="2024-11-12T19:24:11.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{9fb046b4-5758-466a-843f-d9437cae7237}" done="0">
     <x18tc:text xml:space="preserve">2 of 244 patients are in the age range 14 to 24</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="N3" dT="2024-12-17T16:39:11.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{836003d1-2c6f-4773-bb5f-aec1c6b2ec0e}" done="0">
+  <x18tc:threadedComment ref="N3" dT="2024-12-17T16:39:11.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{33677687-a7b1-4d10-bf0f-65e002b98b8f}" done="0">
     <x18tc:text xml:space="preserve">Can be inferred to be adult based on focus on left ventricle</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A13" dT="2024-11-20T19:20:15.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{1e570c19-a6f6-4dc4-bb0c-ce44d2b00afb}" done="0">
+  <x18tc:threadedComment ref="A13" dT="2024-11-20T19:20:15.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{4598e06d-be8d-435f-81fc-c41d6c9b3bff}" done="0">
     <x18tc:text xml:space="preserve">Fitzpatrick17k and HAM1000 have been excluded due to imaging inclusion criteria</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="C8" dT="2024-10-31T15:06:02.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{17b86f2e-263d-4169-a2f5-ed0779a8d0bc}" done="0">
+  <x18tc:threadedComment ref="C8" dT="2024-10-31T15:06:02.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{f0f9173a-37d1-42a7-bce0-1ebb6487be30}" done="0">
     <x18tc:text xml:space="preserve">https://pmc.ncbi.nlm.nih.gov/articles/PMC6367060/
 From 2005 to 2015
 Patients: 103
@@ -16039,7 +16010,7 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="C9" dT="2024-10-31T15:20:00.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{eb327126-4476-48b8-8fd6-79d650932b4b}" done="0">
+  <x18tc:threadedComment ref="C9" dT="2024-10-31T15:20:00.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{0977e7d1-2aa5-4a9b-89c5-d6303bc8d0b1}" done="0">
     <x18tc:text xml:space="preserve">https://pmc.ncbi.nlm.nih.gov/articles/PMC5924623/
 Patients: 148
 Median Age: 63 years
@@ -16075,25 +16046,25 @@
 
 <file path=xl/threadedComments/threadedComment5.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="D16" dT="2024-11-04T16:39:03.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{092211c5-9df5-48e6-a654-e0ae7edc239c}" done="0">
+  <x18tc:threadedComment ref="D16" dT="2024-11-04T16:39:03.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{217ebd8d-2dfb-401e-8155-78c5cb9c7067}" done="0">
     <x18tc:text xml:space="preserve">Same paper as the 2017 BraTS</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="O6" dT="2024-10-29T20:26:14.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{3bdbc492-fbd7-4a41-997a-2b7528574523}" done="0">
+  <x18tc:threadedComment ref="O6" dT="2024-10-29T20:26:14.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{47339414-6e09-47b5-a115-cdd65b3dc56d}" done="0">
     <x18tc:text xml:space="preserve">Unsure if Peds is in dataset, but more than 95% of data is 20 years old and older</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="O20" dT="2024-11-04T18:47:05.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{fbb991a1-3dbd-4a4b-9a30-b219bafcfb26}" done="1">
+  <x18tc:threadedComment ref="O20" dT="2024-11-04T18:47:05.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{5cd4cb81-4718-4606-b17c-c991d4b32a4f}" done="1">
     <x18tc:text xml:space="preserve">Likely adult</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A17" dT="2024-11-04T16:48:15.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{b3d79dc2-a9c3-48b7-8313-7b4359321316}" done="0">
+  <x18tc:threadedComment ref="A17" dT="2024-11-04T16:48:15.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{f0134036-e81d-4f8c-832c-47e5fa6b14ca}" done="0">
     <x18tc:text xml:space="preserve">Paper mentions how morphology of retina of infants and children are different from adults</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="O11" dT="2024-10-31T15:52:41.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{80cc4ac8-b5c9-468f-b39a-aea57aeab627}" done="0">
+  <x18tc:threadedComment ref="O11" dT="2024-10-31T15:52:41.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{62846516-f02f-4f93-a3c5-ccbb741a9126}" done="0">
     <x18tc:text xml:space="preserve">Can be estimated to be Adult (&gt;84%) based on unknown presence of peds data</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="O19" dT="2024-11-04T18:20:39.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{6d8c1669-94e5-4148-8651-8e006fdf0643}" done="1">
+  <x18tc:threadedComment ref="O19" dT="2024-11-04T18:20:39.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{1e22a16e-ff77-4c82-9d37-778797064efc}" done="1">
     <x18tc:text xml:space="preserve">Inferred</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="O12" dT="2024-11-01T18:35:33.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{6f26d3ac-ee71-4f11-bf07-33edb05df08d}" done="1">
+  <x18tc:threadedComment ref="O12" dT="2024-11-01T18:35:33.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{91fcb9c7-cd6b-4e3a-99e5-29bd415d595e}" done="1">
     <x18tc:text xml:space="preserve">Can be inferred to be mostly adult</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -16101,22 +16072,22 @@
 
 <file path=xl/threadedComments/threadedComment6.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="A2" dT="2024-11-27T19:23:31.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{19b86709-d503-43ac-a9a3-18aa966a647f}" done="0">
+  <x18tc:threadedComment ref="A2" dT="2024-11-27T19:23:31.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{0dc8e530-8f38-4506-ba7b-de0f5bc846fd}" done="0">
     <x18tc:text xml:space="preserve">The following datasets are excluded due to lack of metadata available:
 1. COCA
 2. CT Pulmonary Angiography</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A3" dT="2024-11-22T19:02:37.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{26c0d354-cb26-4a29-8bae-0dd9e624c31c}" done="0">
+  <x18tc:threadedComment ref="A3" dT="2024-11-22T19:02:37.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{a69256dd-14fb-4be7-8b98-cd2618432383}" done="0">
     <x18tc:text xml:space="preserve">Filter: Human Demographic Public Complete (41 datasets)
 Excluding Histopathology-only datasets</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A3" dT="2024-11-22T19:12:18.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{7f256f8c-af45-4345-bac9-2e5ecd0f44aa}" parentId="{26c0d354-cb26-4a29-8bae-0dd9e624c31c}">
+  <x18tc:threadedComment ref="A3" dT="2024-11-22T19:12:18.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{0a4e872a-fd69-4dcf-b490-c6886fba0a46}" parentId="{a69256dd-14fb-4be7-8b98-cd2618432383}">
     <x18tc:text xml:space="preserve">Excluded MIDRC datasets since covered above</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A3" dT="2024-11-27T19:08:59.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{fffd1cd8-dd5b-40a6-a649-30861547eded}" parentId="{26c0d354-cb26-4a29-8bae-0dd9e624c31c}">
+  <x18tc:threadedComment ref="A3" dT="2024-11-27T19:08:59.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{6abe2d45-0a98-4d8b-bea6-acf1032cafd8}" parentId="{a69256dd-14fb-4be7-8b98-cd2618432383}">
     <x18tc:text xml:space="preserve">Excluded LungCT-Diagnosis since it didn't have any patient-level demographics</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A3" dT="2024-11-27T19:12:25.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{4ffb2acb-6029-4550-a5ed-e40a02d494b8}" parentId="{26c0d354-cb26-4a29-8bae-0dd9e624c31c}">
+  <x18tc:threadedComment ref="A3" dT="2024-11-27T19:12:25.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{66f052f2-a143-455b-b685-526b9c15d18c}" parentId="{a69256dd-14fb-4be7-8b98-cd2618432383}">
     <x18tc:text xml:space="preserve">Excluded NSCLC-Radiomics-Genomics since it didn't have patient level information</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -16124,7 +16095,7 @@
 
 <file path=xl/threadedComments/threadedComment7.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="A2" dT="2024-11-27T19:24:48.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{f342eddf-cc07-448b-b1cb-bcadaf6e28d3}" done="0">
+  <x18tc:threadedComment ref="A2" dT="2024-11-27T19:24:48.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{161a12f3-f5e1-4b99-a183-957c9e3bc745}" done="0">
     <x18tc:text xml:space="preserve">The following datasets are excluded due to lack of metadata available:
 1. COCA
 2. CT Pulmonary Angiography</x18tc:text>
@@ -16134,17 +16105,17 @@
 
 <file path=xl/threadedComments/threadedComment8.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="A2" dT="2024-11-27T19:26:16.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{6135d8d7-ba59-4340-8cb2-a11766444adf}" done="0">
+  <x18tc:threadedComment ref="A2" dT="2024-11-27T19:26:16.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{4af21bd8-0f21-4a21-bf50-fbcc86efdca4}" done="0">
     <x18tc:text xml:space="preserve">ilter: Human Demographic Public Complete (41 datasets)
 1. Excluding Histopathology-only datasets
 2. Excluded MIDRC datasets since covered above
 3. Excluded LungCT-Diagnosis since it didn't have any patient-level demographics
 4. Excluded NSCLC-Radiomics-Genomics since it didn't have patient level information</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A2" dT="2024-12-19T15:29:12.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{e382f020-9a46-430b-a8cb-c2cc0802eeaf}" parentId="{6135d8d7-ba59-4340-8cb2-a11766444adf}">
+  <x18tc:threadedComment ref="A2" dT="2024-12-19T15:29:12.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{3cd17e96-0234-446a-bc15-7747c801b375}" parentId="{4af21bd8-0f21-4a21-bf50-fbcc86efdca4}">
     <x18tc:text xml:space="preserve">5. Excluded phantom datasets (QIBA-CT-Liver-Phantom)</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="M43" dT="2024-12-19T18:23:14.00" personId="{f023d0ee-96c9-4afc-8a0f-4d12896c8943}" id="{e85e7a11-0851-4ff7-ae24-c893a17606f7}" done="0">
+  <x18tc:threadedComment ref="M43" dT="2024-12-19T18:23:14.00" personId="{0613c3b4-676e-4570-b44e-1d7e620a71c4}" id="{3226d114-5263-4065-93c9-d9c800478e26}" done="0">
     <x18tc:text xml:space="preserve">Estimated from description. Since each patient has 1 pre-treatment and at most 1 follow-up</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -16152,10 +16123,10 @@
 
 <file path=xl/threadedComments/threadedComment9.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="R15" dT="2025-03-17T15:09:37.00" personId="{e7da1d36-66dd-44ad-afd2-ea4a46adf9eb}" id="{4ab1f9cd-9bab-4f57-814b-27e7f7ab1a1b}" done="0">
+  <x18tc:threadedComment ref="R15" dT="2025-03-17T15:09:37.00" personId="{7f9de00e-c95a-4553-a00e-5510805f5b06}" id="{29567dbc-be14-4a52-b8f9-296c952a6c8d}" done="0">
     <x18tc:text xml:space="preserve">This was manually curated. See Repackaging (VQA-RAD) tab</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2025-03-14T15:15:02.00" personId="{e7da1d36-66dd-44ad-afd2-ea4a46adf9eb}" id="{6d4a8d56-2df8-488e-9211-8614a6873217}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2025-03-14T15:15:02.00" personId="{7f9de00e-c95a-4553-a00e-5510805f5b06}" id="{28aa5bc6-a9d2-430c-872b-fbeedf5c1a12}" done="0">
     <x18tc:text xml:space="preserve">2021 QUBIQ challenge was excluded because it didn't specify source of secondary datasets</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -19676,7 +19647,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="3" ht="22.5" hidden="1" customHeight="1">
+    <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="304" t="s">
         <v>935</v>
       </c>
@@ -19818,7 +19789,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="6" ht="22.5" hidden="1" customHeight="1">
+    <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="42" t="s">
         <v>1931</v>
       </c>
@@ -19862,7 +19833,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="7" ht="22.5" hidden="1" customHeight="1">
+    <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="42" t="s">
         <v>1638</v>
       </c>
@@ -19908,7 +19879,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="8" ht="22.5" hidden="1" customHeight="1">
+    <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="330" t="s">
         <v>1688</v>
       </c>
@@ -20142,7 +20113,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="13" ht="22.5" hidden="1" customHeight="1">
+    <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="367" t="s">
         <v>380</v>
       </c>
@@ -20188,7 +20159,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="14" ht="22.5" hidden="1" customHeight="1">
+    <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="367" t="s">
         <v>1892</v>
       </c>
@@ -20230,7 +20201,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="15" ht="22.5" hidden="1" customHeight="1">
+    <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="219" t="s">
         <v>147</v>
       </c>
@@ -20278,7 +20249,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="16" ht="22.5" hidden="1" customHeight="1">
+    <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="367" t="s">
         <v>1971</v>
       </c>
@@ -20318,7 +20289,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="17" ht="22.5" hidden="1" customHeight="1">
+    <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="367" t="s">
         <v>1972</v>
       </c>
@@ -20364,7 +20335,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="18" ht="22.5" hidden="1" customHeight="1">
+    <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="367" t="s">
         <v>1973</v>
       </c>
@@ -20554,7 +20525,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="22" ht="22.5" hidden="1" customHeight="1">
+    <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="367" t="s">
         <v>1988</v>
       </c>
@@ -20688,7 +20659,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="25" ht="22.5" hidden="1" customHeight="1">
+    <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="367" t="s">
         <v>1658</v>
       </c>
@@ -20782,7 +20753,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="27" ht="22.5" hidden="1" customHeight="1">
+    <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="367" t="s">
         <v>1600</v>
       </c>
@@ -39316,7 +39287,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="2" ht="22.5" hidden="1" customHeight="1">
+    <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="219" t="s">
         <v>61</v>
       </c>
@@ -39388,7 +39359,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="3" ht="22.5" hidden="1" customHeight="1">
+    <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="219" t="s">
         <v>123</v>
       </c>
@@ -39450,7 +39421,7 @@
       <c r="Y3" s="6"/>
       <c r="Z3" s="6"/>
     </row>
-    <row r="4" ht="22.5" hidden="1" customHeight="1">
+    <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="219" t="s">
         <v>975</v>
       </c>
@@ -39520,7 +39491,7 @@
       <c r="Y4" s="6"/>
       <c r="Z4" s="6"/>
     </row>
-    <row r="5" ht="22.5" hidden="1" customHeight="1">
+    <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="219" t="s">
         <v>1103</v>
       </c>
@@ -39588,7 +39559,7 @@
       <c r="Y5" s="6"/>
       <c r="Z5" s="6"/>
     </row>
-    <row r="6" ht="22.5" hidden="1" customHeight="1">
+    <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="219" t="s">
         <v>380</v>
       </c>
@@ -39656,7 +39627,7 @@
       <c r="Y6" s="6"/>
       <c r="Z6" s="6"/>
     </row>
-    <row r="7" ht="22.5" hidden="1" customHeight="1">
+    <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="219" t="s">
         <v>151</v>
       </c>
@@ -39726,7 +39697,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="8" ht="22.5" hidden="1" customHeight="1">
+    <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="219" t="s">
         <v>1116</v>
       </c>
@@ -39788,7 +39759,7 @@
       <c r="Y8" s="6"/>
       <c r="Z8" s="6"/>
     </row>
-    <row r="9" ht="22.5" hidden="1" customHeight="1">
+    <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="219" t="s">
         <v>445</v>
       </c>
@@ -39856,7 +39827,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="10" ht="22.5" hidden="1" customHeight="1">
+    <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="219" t="s">
         <v>1125</v>
       </c>
@@ -39924,7 +39895,7 @@
       <c r="Y10" s="6"/>
       <c r="Z10" s="6"/>
     </row>
-    <row r="11" ht="22.5" hidden="1" customHeight="1">
+    <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="219" t="s">
         <v>415</v>
       </c>
@@ -39988,7 +39959,7 @@
       <c r="Y11" s="6"/>
       <c r="Z11" s="6"/>
     </row>
-    <row r="12" ht="22.5" hidden="1" customHeight="1">
+    <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="219" t="s">
         <v>1147</v>
       </c>
@@ -40052,7 +40023,7 @@
       <c r="Y12" s="6"/>
       <c r="Z12" s="6"/>
     </row>
-    <row r="13" ht="22.5" hidden="1" customHeight="1">
+    <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="219" t="s">
         <v>227</v>
       </c>
@@ -40124,7 +40095,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="14" ht="22.5" hidden="1" customHeight="1">
+    <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="219" t="s">
         <v>1154</v>
       </c>
@@ -40254,7 +40225,7 @@
       <c r="Y15" s="6"/>
       <c r="Z15" s="6"/>
     </row>
-    <row r="16" ht="22.5" hidden="1" customHeight="1">
+    <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="219" t="s">
         <v>1168</v>
       </c>
@@ -40320,7 +40291,7 @@
       <c r="Y16" s="6"/>
       <c r="Z16" s="6"/>
     </row>
-    <row r="17" ht="22.5" hidden="1" customHeight="1">
+    <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="219" t="s">
         <v>1175</v>
       </c>
@@ -40384,7 +40355,7 @@
       <c r="Y17" s="6"/>
       <c r="Z17" s="6"/>
     </row>
-    <row r="18" ht="22.5" hidden="1" customHeight="1">
+    <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="219" t="s">
         <v>1181</v>
       </c>
@@ -40446,7 +40417,7 @@
       <c r="Y18" s="6"/>
       <c r="Z18" s="6"/>
     </row>
-    <row r="19" ht="22.5" hidden="1" customHeight="1">
+    <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="219" t="s">
         <v>990</v>
       </c>
@@ -40510,7 +40481,7 @@
       <c r="Y19" s="6"/>
       <c r="Z19" s="6"/>
     </row>
-    <row r="20" ht="22.5" hidden="1" customHeight="1">
+    <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="219" t="s">
         <v>1190</v>
       </c>
@@ -40576,7 +40547,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="21" ht="22.5" hidden="1" customHeight="1">
+    <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="219" t="s">
         <v>1198</v>
       </c>
@@ -40640,7 +40611,7 @@
       <c r="Y21" s="6"/>
       <c r="Z21" s="6"/>
     </row>
-    <row r="22" ht="22.5" hidden="1" customHeight="1">
+    <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="219" t="s">
         <v>1204</v>
       </c>
@@ -40708,7 +40679,7 @@
       <c r="Y22" s="6"/>
       <c r="Z22" s="6"/>
     </row>
-    <row r="23" ht="22.5" hidden="1" customHeight="1">
+    <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="219" t="s">
         <v>1210</v>
       </c>
@@ -40774,7 +40745,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="24" ht="22.5" hidden="1" customHeight="1">
+    <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="219" t="s">
         <v>248</v>
       </c>
@@ -40832,7 +40803,7 @@
       <c r="Y24" s="6"/>
       <c r="Z24" s="6"/>
     </row>
-    <row r="25" ht="22.5" hidden="1" customHeight="1">
+    <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="219" t="s">
         <v>1217</v>
       </c>
@@ -40894,7 +40865,7 @@
       <c r="Y25" s="6"/>
       <c r="Z25" s="6"/>
     </row>
-    <row r="26" ht="22.5" hidden="1" customHeight="1">
+    <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="219" t="s">
         <v>503</v>
       </c>
@@ -40960,7 +40931,7 @@
       <c r="Y26" s="6"/>
       <c r="Z26" s="6"/>
     </row>
-    <row r="27" ht="22.5" hidden="1" customHeight="1">
+    <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="219" t="s">
         <v>1227</v>
       </c>
@@ -41028,7 +40999,7 @@
       <c r="Y27" s="6"/>
       <c r="Z27" s="6"/>
     </row>
-    <row r="28" ht="22.5" hidden="1" customHeight="1">
+    <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="219" t="s">
         <v>364</v>
       </c>
@@ -41092,7 +41063,7 @@
       <c r="Y28" s="6"/>
       <c r="Z28" s="6"/>
     </row>
-    <row r="29" ht="22.5" hidden="1" customHeight="1">
+    <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="219" t="s">
         <v>1239</v>
       </c>
@@ -41158,7 +41129,7 @@
       <c r="Y29" s="6"/>
       <c r="Z29" s="6"/>
     </row>
-    <row r="30" ht="22.5" hidden="1" customHeight="1">
+    <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="219" t="s">
         <v>1246</v>
       </c>
@@ -41222,7 +41193,7 @@
       <c r="Y30" s="6"/>
       <c r="Z30" s="6"/>
     </row>
-    <row r="31" ht="22.5" hidden="1" customHeight="1">
+    <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="219" t="s">
         <v>1254</v>
       </c>
@@ -41696,7 +41667,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="2" ht="22.5" hidden="1" customHeight="1">
+    <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>315</v>
       </c>
@@ -41753,7 +41724,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="3" ht="22.5" hidden="1" customHeight="1">
+    <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="6"/>
       <c r="B3" s="239" t="s">
         <v>1190</v>
@@ -41802,7 +41773,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="4" ht="22.5" hidden="1" customHeight="1">
+    <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="6"/>
       <c r="B4" s="239" t="s">
         <v>1291</v>
@@ -42053,7 +42024,7 @@
       </c>
       <c r="S8" s="6"/>
     </row>
-    <row r="9" ht="22.5" hidden="1" customHeight="1">
+    <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="6"/>
       <c r="B9" s="239" t="s">
         <v>1322</v>
@@ -42108,7 +42079,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="10" ht="22.5" hidden="1" customHeight="1">
+    <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="6"/>
       <c r="B10" s="239" t="s">
         <v>1330</v>
@@ -42157,7 +42128,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="11" ht="22.5" hidden="1" customHeight="1">
+    <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="6"/>
       <c r="B11" s="239" t="s">
         <v>1337</v>
@@ -42208,7 +42179,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="12" ht="22.5" hidden="1" customHeight="1">
+    <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="239" t="s">
         <v>1343</v>
@@ -42261,7 +42232,7 @@
       </c>
       <c r="S12" s="6"/>
     </row>
-    <row r="13" ht="22.5" hidden="1" customHeight="1">
+    <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="6"/>
       <c r="B13" s="239" t="s">
         <v>1350</v>
